--- a/artfynd/A 6969-2023 artfynd.xlsx
+++ b/artfynd/A 6969-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6969-2023 artfynd.xlsx
+++ b/artfynd/A 6969-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110076999</v>
+        <v>115983198</v>
       </c>
       <c r="B2" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kroenenaesie, Ås lm</t>
+          <t>Dikanäs - Kittelfjäll, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531593.2663653565</v>
+        <v>531678</v>
       </c>
       <c r="R2" t="n">
-        <v>7238329.884282734</v>
+        <v>7238363</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,21 +743,11 @@
           <t>2023-06-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-06-14</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -772,53 +756,57 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>5414</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Rickard Gustafsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115983193</v>
+        <v>115983204</v>
       </c>
       <c r="B3" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531673</v>
+        <v>531667</v>
       </c>
       <c r="R3" t="n">
-        <v>7238366</v>
+        <v>7238361</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,7 +865,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -888,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -899,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115983245</v>
+        <v>115983222</v>
       </c>
       <c r="B4" t="n">
-        <v>74652</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531487</v>
+        <v>531660</v>
       </c>
       <c r="R4" t="n">
-        <v>7238334</v>
+        <v>7238344</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -988,7 +971,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1010,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115983222</v>
+        <v>115983294</v>
       </c>
       <c r="B5" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,12 +1013,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1050,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>531660</v>
+        <v>531574</v>
       </c>
       <c r="R5" t="n">
-        <v>7238344</v>
+        <v>7238244</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,7 +1077,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1121,37 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115983288</v>
+        <v>115983293</v>
       </c>
       <c r="B6" t="n">
-        <v>94068</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1161,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>531513</v>
+        <v>531573</v>
       </c>
       <c r="R6" t="n">
-        <v>7238272</v>
+        <v>7238245</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,7 +1183,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1221,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1232,37 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115983199</v>
+        <v>115983245</v>
       </c>
       <c r="B7" t="n">
-        <v>74632</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1272,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>531666</v>
+        <v>531487</v>
       </c>
       <c r="R7" t="n">
-        <v>7238363</v>
+        <v>7238334</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,7 +1289,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1332,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1343,15 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115983208</v>
+        <v>115983191</v>
       </c>
       <c r="B8" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>531658</v>
+        <v>531674</v>
       </c>
       <c r="R8" t="n">
-        <v>7238357</v>
+        <v>7238368</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,7 +1395,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1443,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1454,37 +1417,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115983294</v>
+        <v>115983212</v>
       </c>
       <c r="B9" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>531574</v>
+        <v>531655</v>
       </c>
       <c r="R9" t="n">
-        <v>7238244</v>
+        <v>7238348</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1543,7 +1501,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>5388</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1554,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1565,37 +1523,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115983296</v>
+        <v>115983248</v>
       </c>
       <c r="B10" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1605,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>531567</v>
+        <v>531576</v>
       </c>
       <c r="R10" t="n">
-        <v>7238241</v>
+        <v>7238332</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1654,7 +1607,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1665,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1676,15 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115983212</v>
+        <v>115983288</v>
       </c>
       <c r="B11" t="n">
-        <v>94068</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>531655</v>
+        <v>531513</v>
       </c>
       <c r="R11" t="n">
-        <v>7238348</v>
+        <v>7238272</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1765,7 +1713,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1787,37 +1735,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115983198</v>
+        <v>115983208</v>
       </c>
       <c r="B12" t="n">
-        <v>74640</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1827,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>531678</v>
+        <v>531658</v>
       </c>
       <c r="R12" t="n">
-        <v>7238363</v>
+        <v>7238357</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1876,7 +1819,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>5406</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1898,37 +1841,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115983191</v>
+        <v>115983238</v>
       </c>
       <c r="B13" t="n">
-        <v>79559</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1938,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>531674</v>
+        <v>531496</v>
       </c>
       <c r="R13" t="n">
-        <v>7238368</v>
+        <v>7238340</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1987,7 +1925,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1998,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2009,37 +1947,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115983293</v>
+        <v>115983291</v>
       </c>
       <c r="B14" t="n">
-        <v>90341</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>531573</v>
+        <v>531506</v>
       </c>
       <c r="R14" t="n">
-        <v>7238245</v>
+        <v>7238261</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2098,7 +2031,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2109,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Robin Karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2120,15 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115983196</v>
+        <v>110076999</v>
       </c>
       <c r="B15" t="n">
-        <v>74632</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2154,19 +2082,20 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
+          <t>Kroenenaesie, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>531678</v>
+        <v>531593</v>
       </c>
       <c r="R15" t="n">
-        <v>7238364</v>
+        <v>7238330</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2193,11 +2122,21 @@
           <t>2023-06-14</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-06-14</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2206,40 +2145,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>5417</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Rickard Gustafsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115983261</v>
+        <v>115983196</v>
       </c>
       <c r="B16" t="n">
-        <v>74632</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2271,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>531580</v>
+        <v>531678</v>
       </c>
       <c r="R16" t="n">
-        <v>7238320</v>
+        <v>7238364</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2320,7 +2245,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>5394</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2342,15 +2267,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115983248</v>
+        <v>115983199</v>
       </c>
       <c r="B17" t="n">
-        <v>94068</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2358,21 +2278,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2809</v>
+        <v>6439</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2382,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>531576</v>
+        <v>531666</v>
       </c>
       <c r="R17" t="n">
-        <v>7238332</v>
+        <v>7238363</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2431,7 +2351,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2453,37 +2373,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115983291</v>
+        <v>115983261</v>
       </c>
       <c r="B18" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2493,10 +2408,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>531506</v>
+        <v>531580</v>
       </c>
       <c r="R18" t="n">
-        <v>7238261</v>
+        <v>7238320</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2542,7 +2457,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5394</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2564,37 +2479,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115983204</v>
+        <v>115983193</v>
       </c>
       <c r="B19" t="n">
-        <v>74640</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2604,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>531667</v>
+        <v>531673</v>
       </c>
       <c r="R19" t="n">
-        <v>7238361</v>
+        <v>7238366</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2653,7 +2563,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2664,121 +2574,10 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Robin Karlsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>115983238</v>
-      </c>
-      <c r="B20" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Dikanäs - Kittelfjäll, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>531496</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7238340</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>5390</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Robin Karlsson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
         <is>
           <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
         </is>
